--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-18).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-18).xlsx
@@ -935,49 +935,52 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 8.752,75</t>
-  </si>
-  <si>
-    <t>92.8</t>
-  </si>
-  <si>
-    <t>63.2</t>
-  </si>
-  <si>
-    <t>5.94</t>
-  </si>
-  <si>
-    <t>20.3</t>
-  </si>
-  <si>
-    <t>7.6</t>
-  </si>
-  <si>
-    <t>5.9</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 8.785,26</t>
+  </si>
+  <si>
+    <t>93.1</t>
+  </si>
+  <si>
+    <t>63.1</t>
+  </si>
+  <si>
+    <t>6.00</t>
+  </si>
+  <si>
+    <t>20.4</t>
+  </si>
+  <si>
+    <t>7.7</t>
+  </si>
+  <si>
+    <t>6.0</t>
   </si>
   <si>
     <t>34.6%</t>
   </si>
   <si>
-    <t>17.3%</t>
+    <t>17.2%</t>
   </si>
   <si>
     <t>1.3%</t>
   </si>
   <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>6.4%</t>
+    <t>6.3%</t>
   </si>
   <si>
     <t>2.2%</t>
@@ -986,34 +989,34 @@
     <t>5.7%</t>
   </si>
   <si>
-    <t>2323.0</t>
-  </si>
-  <si>
-    <t>1925.0</t>
-  </si>
-  <si>
-    <t>139.0</t>
-  </si>
-  <si>
-    <t>24.0</t>
-  </si>
-  <si>
-    <t>403.0</t>
-  </si>
-  <si>
-    <t>123.0</t>
+    <t>2351.0</t>
+  </si>
+  <si>
+    <t>1948.0</t>
+  </si>
+  <si>
+    <t>142.0</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>405.0</t>
+  </si>
+  <si>
+    <t>127.0</t>
   </si>
   <si>
     <t>22.0</t>
   </si>
   <si>
-    <t>712.0</t>
+    <t>717.0</t>
   </si>
   <si>
     <t>250.0</t>
   </si>
   <si>
-    <t>631.0</t>
+    <t>645.0</t>
   </si>
   <si>
     <t>0.4%</t>
@@ -7618,7 +7621,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7648,35 +7651,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>11495.01</v>
+      </c>
+      <c r="N42" s="6">
+        <v>114</v>
+      </c>
+      <c r="O42" s="6">
+        <v>91</v>
+      </c>
+      <c r="P42" s="7">
+        <v>10.918233333333333</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>33.957875824175829</v>
+      </c>
+      <c r="R42" s="8">
+        <v>15.1837</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.13186813186813187</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.098901098901098897</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.01098901098901099</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0.065934065934065936</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -10004,7 +10065,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10034,14 +10095,26 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>11248.040000000001</v>
+      </c>
+      <c r="N58" s="6">
+        <v>129</v>
+      </c>
       <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>4.765079365079365</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>19.319203260869564</v>
+      </c>
+      <c r="R58" s="8">
+        <v>7.1548913043478262</v>
+      </c>
       <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.34782608695652173</v>
+      </c>
       <c r="U58" s="9"/>
       <c r="V58" s="9"/>
       <c r="W58" s="9"/>
@@ -16466,7 +16539,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16496,35 +16569,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>8033.5900000000001</v>
+      </c>
+      <c r="N102" s="6">
+        <v>79</v>
+      </c>
+      <c r="O102" s="6">
+        <v>64</v>
+      </c>
+      <c r="P102" s="7">
+        <v>13.792073170731708</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>32.858332812500002</v>
+      </c>
+      <c r="R102" s="8">
+        <v>13.857778333333332</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.078125</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.21875</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.015625</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.078125</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -17737,7 +17868,9 @@
       <c r="N111" s="6">
         <v>31</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>29</v>
+      </c>
       <c r="P111" s="7">
         <v>5.4037645161290317</v>
       </c>
@@ -17747,31 +17880,75 @@
       <c r="R111" s="8">
         <v>0.99310344827586206</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.75862068965517238</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -30241,7 +30418,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30271,14 +30448,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>10215.82</v>
+      </c>
+      <c r="N195" s="6">
+        <v>107</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>5.7626168224299068</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>19.646171621621622</v>
+      </c>
+      <c r="R195" s="8">
+        <v>6.5700445945945942</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.25675675675675674</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>
@@ -33014,52 +33203,52 @@
         <v>321</v>
       </c>
       <c t="s" r="Z216" s="11">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="AA216" s="11">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="AB216" s="11">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="AC216" s="11">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="AD216" s="11">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="AE216" s="11">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="AF216" s="11">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="AG216" s="11">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="AH216" s="11">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="AI216" s="11">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="AJ216" s="11">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="AK216" s="11">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="AL216" s="11">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="AM216" s="11">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="AN216" s="11">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c t="s" r="AO216" s="11">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -33076,10 +33265,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-18).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-18).xlsx
@@ -935,16 +935,16 @@
     <t>214</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 8.785,26</t>
-  </si>
-  <si>
-    <t>93.1</t>
-  </si>
-  <si>
-    <t>63.1</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 8.803,72</t>
+  </si>
+  <si>
+    <t>93.3</t>
+  </si>
+  <si>
+    <t>63.5</t>
   </si>
   <si>
     <t>6.00</t>
@@ -956,10 +956,10 @@
     <t>7.7</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>34.6%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>33.8%</t>
   </si>
   <si>
     <t>17.2%</t>
@@ -968,7 +968,7 @@
     <t>1.3%</t>
   </si>
   <si>
-    <t>0.3%</t>
+    <t>0.2%</t>
   </si>
   <si>
     <t>3.6%</t>
@@ -977,10 +977,7 @@
     <t>1.1%</t>
   </si>
   <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>6.3%</t>
+    <t>6.2%</t>
   </si>
   <si>
     <t>2.2%</t>
@@ -989,40 +986,40 @@
     <t>5.7%</t>
   </si>
   <si>
-    <t>2351.0</t>
-  </si>
-  <si>
-    <t>1948.0</t>
-  </si>
-  <si>
-    <t>142.0</t>
+    <t>2408.0</t>
+  </si>
+  <si>
+    <t>2001.0</t>
+  </si>
+  <si>
+    <t>146.0</t>
   </si>
   <si>
     <t>29.0</t>
   </si>
   <si>
-    <t>405.0</t>
-  </si>
-  <si>
-    <t>127.0</t>
+    <t>413.0</t>
+  </si>
+  <si>
+    <t>128.0</t>
   </si>
   <si>
     <t>22.0</t>
   </si>
   <si>
-    <t>717.0</t>
-  </si>
-  <si>
-    <t>250.0</t>
-  </si>
-  <si>
-    <t>645.0</t>
+    <t>726.0</t>
+  </si>
+  <si>
+    <t>257.0</t>
+  </si>
+  <si>
+    <t>666.0</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>43.0</t>
+    <t>50.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3278,7 +3275,9 @@
       <c r="N13" s="6">
         <v>141</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>116</v>
+      </c>
       <c r="P13" s="7">
         <v>7.4361680272108845</v>
       </c>
@@ -3288,31 +3287,75 @@
       <c r="R13" s="8">
         <v>9.7954025862068956</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
       <c r="T13" s="9">
         <v>0.13793103448275862</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="U13" s="9">
+        <v>0.19827586206896552</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.025862068965517241</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0.0086206896551724137</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.043103448275862072</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>24</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>23</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.060344827586206899</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>7</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -10101,7 +10144,9 @@
       <c r="N58" s="6">
         <v>129</v>
       </c>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>92</v>
+      </c>
       <c r="P58" s="7">
         <v>4.765079365079365</v>
       </c>
@@ -10111,31 +10156,75 @@
       <c r="R58" s="8">
         <v>7.1548913043478262</v>
       </c>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9">
         <v>0.34782608695652173</v>
       </c>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.010869565217391304</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.010869565217391304</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -12711,7 +12800,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12739,35 +12828,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>12201.059999999999</v>
+      </c>
+      <c r="N76" s="6">
+        <v>134</v>
+      </c>
+      <c r="O76" s="6">
+        <v>69</v>
+      </c>
+      <c r="P76" s="7">
+        <v>5.3202205882352942</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>21.70193188405797</v>
+      </c>
+      <c r="R76" s="8">
+        <v>8.0582046153846161</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.15942028985507245</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.40579710144927539</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.11594202898550725</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.028985507246376812</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.24637681159420291</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>31</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>28</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>17</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -28050,7 +28197,9 @@
       <c r="N179" s="6">
         <v>87</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>44</v>
+      </c>
       <c r="P179" s="7">
         <v>3.4662741176470591</v>
       </c>
@@ -28060,31 +28209,75 @@
       <c r="R179" s="8">
         <v>1.2321977272727274</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.90909090909090906</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
@@ -33203,52 +33396,52 @@
         <v>321</v>
       </c>
       <c t="s" r="Z216" s="11">
+        <v>319</v>
+      </c>
+      <c t="s" r="AA216" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="AB216" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="AC216" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AD216" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AE216" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AF216" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AG216" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AH216" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AI216" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AJ216" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AK216" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AL216" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AM216" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AN216" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AO216" s="11">
         <v>336</v>
-      </c>
-      <c t="s" r="AO216" s="11">
-        <v>337</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -33265,10 +33458,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-18).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-18).xlsx
@@ -935,10 +935,10 @@
     <t>214</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 8.803,72</t>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 8.807,27</t>
   </si>
   <si>
     <t>93.3</t>
@@ -947,7 +947,7 @@
     <t>63.5</t>
   </si>
   <si>
-    <t>6.00</t>
+    <t>5.99</t>
   </si>
   <si>
     <t>20.4</t>
@@ -959,7 +959,7 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>33.8%</t>
+    <t>34.0%</t>
   </si>
   <si>
     <t>17.2%</t>
@@ -4958,7 +4958,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4988,14 +4988,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>9005.9300000000003</v>
+      </c>
+      <c r="N24" s="6">
+        <v>100</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>5.7928571428571436</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>22.329577464788734</v>
+      </c>
+      <c r="R24" s="8">
+        <v>9.4881637681159425</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.21126760563380281</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -14773,7 +14785,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14801,14 +14813,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>9264.8799999999992</v>
+      </c>
+      <c r="N89" s="6">
+        <v>81</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>5.5650402439024393</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>18.689248387096775</v>
+      </c>
+      <c r="R89" s="8">
+        <v>4.5016129032258068</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.29032258064516131</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
